--- a/output/Tables/Best practice/Residence/HIA_best_practice_1000replicate_RES.xlsx
+++ b/output/Tables/Best practice/Residence/HIA_best_practice_1000replicate_RES.xlsx
@@ -438,22 +438,22 @@
         </is>
       </c>
       <c r="C2">
-        <v>29173.533</v>
+        <v>29176.23</v>
       </c>
       <c r="D2">
-        <v>27082.593</v>
+        <v>27088.379</v>
       </c>
       <c r="E2">
-        <v>31262.074</v>
+        <v>31267.245</v>
       </c>
       <c r="F2">
-        <v>253106.412</v>
+        <v>253133.959</v>
       </c>
       <c r="G2">
-        <v>242154.31</v>
+        <v>242201.034</v>
       </c>
       <c r="H2">
-        <v>264058.321</v>
+        <v>264095.48</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -465,13 +465,13 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>33662572720.103</v>
+        <v>33667455071.95</v>
       </c>
       <c r="M2">
-        <v>32202868298.703</v>
+        <v>32208838105.116</v>
       </c>
       <c r="N2">
-        <v>35121277309.403</v>
+        <v>35122854057.599</v>
       </c>
     </row>
     <row r="3">
@@ -486,22 +486,22 @@
         </is>
       </c>
       <c r="C3">
-        <v>27792.853</v>
+        <v>27789.281</v>
       </c>
       <c r="D3">
-        <v>26009.454</v>
+        <v>26006.518</v>
       </c>
       <c r="E3">
-        <v>29565.791</v>
+        <v>29562.536</v>
       </c>
       <c r="F3">
-        <v>251619.129</v>
+        <v>251607.939</v>
       </c>
       <c r="G3">
-        <v>242312.393</v>
+        <v>242294.403</v>
       </c>
       <c r="H3">
-        <v>260913.348</v>
+        <v>260900.023</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -513,13 +513,13 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>33463572963.909</v>
+        <v>33461688390.11</v>
       </c>
       <c r="M3">
-        <v>32221490160.416</v>
+        <v>32221119532.697</v>
       </c>
       <c r="N3">
-        <v>34713678271.714</v>
+        <v>34710302221.23</v>
       </c>
     </row>
     <row r="4">
@@ -534,22 +534,22 @@
         </is>
       </c>
       <c r="C4">
-        <v>39958.621</v>
+        <v>39967.751</v>
       </c>
       <c r="D4">
-        <v>37382.413</v>
+        <v>37390.867</v>
       </c>
       <c r="E4">
-        <v>42530.763</v>
+        <v>42534.536</v>
       </c>
       <c r="F4">
-        <v>404929.436</v>
+        <v>404944.176</v>
       </c>
       <c r="G4">
-        <v>390334.585</v>
+        <v>390369.076</v>
       </c>
       <c r="H4">
-        <v>419520.98</v>
+        <v>419563.352</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -561,13 +561,13 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>53863214118.965</v>
+        <v>53866649964.591</v>
       </c>
       <c r="M4">
-        <v>51918359333.588</v>
+        <v>51911231747.49</v>
       </c>
       <c r="N4">
-        <v>55814375963.823</v>
+        <v>55827230236.291</v>
       </c>
     </row>
     <row r="5">
@@ -582,40 +582,40 @@
         </is>
       </c>
       <c r="C5">
-        <v>15192.64</v>
+        <v>15213.58</v>
       </c>
       <c r="D5">
-        <v>14342.44</v>
+        <v>14358.14</v>
       </c>
       <c r="E5">
-        <v>16053.555</v>
+        <v>16080.12</v>
       </c>
       <c r="F5">
-        <v>11798.585</v>
+        <v>11814.665</v>
       </c>
       <c r="G5">
-        <v>11192.939</v>
+        <v>11206.827</v>
       </c>
       <c r="H5">
-        <v>12411.138</v>
+        <v>12428.765</v>
       </c>
       <c r="I5">
-        <v>846418413.271</v>
+        <v>847463911.3380001</v>
       </c>
       <c r="J5">
-        <v>798868194.696</v>
+        <v>799699341.012</v>
       </c>
       <c r="K5">
-        <v>894126449.375</v>
+        <v>895560733.051</v>
       </c>
       <c r="L5">
-        <v>1569202068.095</v>
+        <v>1571338018.892</v>
       </c>
       <c r="M5">
-        <v>1488242322.983</v>
+        <v>1490599066.52</v>
       </c>
       <c r="N5">
-        <v>1650729365.623</v>
+        <v>1652932821.965</v>
       </c>
     </row>
     <row r="6">
@@ -630,40 +630,40 @@
         </is>
       </c>
       <c r="C6">
-        <v>13423.212</v>
+        <v>13435.807</v>
       </c>
       <c r="D6">
-        <v>12759.367</v>
+        <v>12769.084</v>
       </c>
       <c r="E6">
-        <v>14092.386</v>
+        <v>14110.095</v>
       </c>
       <c r="F6">
-        <v>10743.006</v>
+        <v>10749.918</v>
       </c>
       <c r="G6">
-        <v>10254.615</v>
+        <v>10259.918</v>
       </c>
       <c r="H6">
-        <v>11236.886</v>
+        <v>11247.499</v>
       </c>
       <c r="I6">
-        <v>747812197.036</v>
+        <v>748526928.141</v>
       </c>
       <c r="J6">
-        <v>710750217.789</v>
+        <v>711414814.402</v>
       </c>
       <c r="K6">
-        <v>785310871.053</v>
+        <v>786054082.812</v>
       </c>
       <c r="L6">
-        <v>1428940166.651</v>
+        <v>1429817786.404</v>
       </c>
       <c r="M6">
-        <v>1364153633.91</v>
+        <v>1364589783.668</v>
       </c>
       <c r="N6">
-        <v>1494699705.69</v>
+        <v>1495956502.87</v>
       </c>
     </row>
     <row r="7">
@@ -678,40 +678,40 @@
         </is>
       </c>
       <c r="C7">
-        <v>24030.356</v>
+        <v>24041.56</v>
       </c>
       <c r="D7">
-        <v>22809.119</v>
+        <v>22822.8</v>
       </c>
       <c r="E7">
-        <v>25266.223</v>
+        <v>25276.5</v>
       </c>
       <c r="F7">
-        <v>20354.4</v>
+        <v>20368.632</v>
       </c>
       <c r="G7">
-        <v>19465.958</v>
+        <v>19479.353</v>
       </c>
       <c r="H7">
-        <v>21256.97</v>
+        <v>21265.563</v>
       </c>
       <c r="I7">
-        <v>1338714285.228</v>
+        <v>1339193519.068</v>
       </c>
       <c r="J7">
-        <v>1270347024.583</v>
+        <v>1270940002.323</v>
       </c>
       <c r="K7">
-        <v>1407627187.652</v>
+        <v>1408410092.38</v>
       </c>
       <c r="L7">
-        <v>2707264902.043</v>
+        <v>2709160040.966</v>
       </c>
       <c r="M7">
-        <v>2589248159.682</v>
+        <v>2590790931.532</v>
       </c>
       <c r="N7">
-        <v>2826946792.73</v>
+        <v>2828960507.208</v>
       </c>
     </row>
     <row r="8">
@@ -726,40 +726,40 @@
         </is>
       </c>
       <c r="C8">
-        <v>7450.168</v>
+        <v>7445.826</v>
       </c>
       <c r="D8">
-        <v>7081.575</v>
+        <v>7075.912</v>
       </c>
       <c r="E8">
-        <v>7825.006</v>
+        <v>7823.749</v>
       </c>
       <c r="F8">
-        <v>8885.978999999999</v>
+        <v>8887.757</v>
       </c>
       <c r="G8">
-        <v>8398.293</v>
+        <v>8400.766</v>
       </c>
       <c r="H8">
-        <v>9387.512000000001</v>
+        <v>9391.992</v>
       </c>
       <c r="I8">
-        <v>110300867.684</v>
+        <v>110226530.035</v>
       </c>
       <c r="J8">
-        <v>104827831.391</v>
+        <v>104777336.802</v>
       </c>
       <c r="K8">
-        <v>115839780.963</v>
+        <v>115811243.351</v>
       </c>
       <c r="L8">
-        <v>1181835698.961</v>
+        <v>1182009748.605</v>
       </c>
       <c r="M8">
-        <v>1116830946.488</v>
+        <v>1117053942.812</v>
       </c>
       <c r="N8">
-        <v>1248181023.556</v>
+        <v>1249239710.325</v>
       </c>
     </row>
     <row r="9">
@@ -774,40 +774,40 @@
         </is>
       </c>
       <c r="C9">
-        <v>6387.076</v>
+        <v>6389.522</v>
       </c>
       <c r="D9">
-        <v>6108.993</v>
+        <v>6111.595</v>
       </c>
       <c r="E9">
-        <v>6671.17</v>
+        <v>6669.555</v>
       </c>
       <c r="F9">
-        <v>7896.411</v>
+        <v>7909.374</v>
       </c>
       <c r="G9">
-        <v>7511.41</v>
+        <v>7525.415</v>
       </c>
       <c r="H9">
-        <v>8291.429</v>
+        <v>8301.477999999999</v>
       </c>
       <c r="I9">
-        <v>94561729.85699999</v>
+        <v>94604018.388</v>
       </c>
       <c r="J9">
-        <v>90468093.293</v>
+        <v>90503068.92200001</v>
       </c>
       <c r="K9">
-        <v>98804158.31299999</v>
+        <v>98764991.411</v>
       </c>
       <c r="L9">
-        <v>1050211974.325</v>
+        <v>1051885432.585</v>
       </c>
       <c r="M9">
-        <v>999019963.336</v>
+        <v>1000698244.372</v>
       </c>
       <c r="N9">
-        <v>1103207363.81</v>
+        <v>1104344649.063</v>
       </c>
     </row>
     <row r="10">
@@ -822,40 +822,40 @@
         </is>
       </c>
       <c r="C10">
-        <v>14200.726</v>
+        <v>14201.711</v>
       </c>
       <c r="D10">
-        <v>13605.345</v>
+        <v>13608.942</v>
       </c>
       <c r="E10">
-        <v>14804.074</v>
+        <v>14804.059</v>
       </c>
       <c r="F10">
-        <v>20213.652</v>
+        <v>20252.04</v>
       </c>
       <c r="G10">
-        <v>19255.432</v>
+        <v>19294.185</v>
       </c>
       <c r="H10">
-        <v>21184.152</v>
+        <v>21230.882</v>
       </c>
       <c r="I10">
-        <v>210266667.318</v>
+        <v>210285071.55</v>
       </c>
       <c r="J10">
-        <v>201375499.988</v>
+        <v>201525769.428</v>
       </c>
       <c r="K10">
-        <v>219253859.763</v>
+        <v>219238264.121</v>
       </c>
       <c r="L10">
-        <v>2688202750.128</v>
+        <v>2693489628.516</v>
       </c>
       <c r="M10">
-        <v>2561148726.392</v>
+        <v>2566945132.571</v>
       </c>
       <c r="N10">
-        <v>2816640578.632</v>
+        <v>2823252581.91</v>
       </c>
     </row>
     <row r="11">
@@ -870,40 +870,40 @@
         </is>
       </c>
       <c r="C11">
-        <v>1446.811</v>
+        <v>1448.396</v>
       </c>
       <c r="D11">
-        <v>1363.796</v>
+        <v>1364.578</v>
       </c>
       <c r="E11">
-        <v>1531.566</v>
+        <v>1535.15</v>
       </c>
       <c r="F11">
-        <v>2413.361</v>
+        <v>2413.044</v>
       </c>
       <c r="G11">
-        <v>2276.645</v>
+        <v>2275.871</v>
       </c>
       <c r="H11">
-        <v>2553.617</v>
+        <v>2555.936</v>
       </c>
       <c r="I11">
-        <v>108788761.332</v>
+        <v>108931845.393</v>
       </c>
       <c r="J11">
-        <v>102547100.791</v>
+        <v>102592522.849</v>
       </c>
       <c r="K11">
-        <v>115238685.269</v>
+        <v>115413891.95</v>
       </c>
       <c r="L11">
-        <v>321024576.668</v>
+        <v>320944308.248</v>
       </c>
       <c r="M11">
-        <v>302781440.732</v>
+        <v>302596146.279</v>
       </c>
       <c r="N11">
-        <v>339582650.551</v>
+        <v>339952237.555</v>
       </c>
     </row>
     <row r="12">
@@ -918,40 +918,40 @@
         </is>
       </c>
       <c r="C12">
-        <v>1271.432</v>
+        <v>1274.001</v>
       </c>
       <c r="D12">
-        <v>1206.614</v>
+        <v>1208.759</v>
       </c>
       <c r="E12">
-        <v>1337.786</v>
+        <v>1340.305</v>
       </c>
       <c r="F12">
-        <v>2194.465</v>
+        <v>2197.96</v>
       </c>
       <c r="G12">
-        <v>2083.835</v>
+        <v>2086.047</v>
       </c>
       <c r="H12">
-        <v>2308.486</v>
+        <v>2311.59</v>
       </c>
       <c r="I12">
-        <v>95625323.086</v>
+        <v>95815025.605</v>
       </c>
       <c r="J12">
-        <v>90772718.064</v>
+        <v>90931284.80500001</v>
       </c>
       <c r="K12">
-        <v>100616394.253</v>
+        <v>100779757.055</v>
       </c>
       <c r="L12">
-        <v>291853714.206</v>
+        <v>292290181.326</v>
       </c>
       <c r="M12">
-        <v>277141077.149</v>
+        <v>277457157.266</v>
       </c>
       <c r="N12">
-        <v>307063252.201</v>
+        <v>307500192.317</v>
       </c>
     </row>
     <row r="13">
@@ -966,40 +966,40 @@
         </is>
       </c>
       <c r="C13">
-        <v>2856.317</v>
+        <v>2858.089</v>
       </c>
       <c r="D13">
-        <v>2722.292</v>
+        <v>2724.016</v>
       </c>
       <c r="E13">
-        <v>2992.823</v>
+        <v>2994.577</v>
       </c>
       <c r="F13">
-        <v>5535.856</v>
+        <v>5534.245</v>
       </c>
       <c r="G13">
-        <v>5272.972</v>
+        <v>5269.802</v>
       </c>
       <c r="H13">
-        <v>5805.772</v>
+        <v>5802.785</v>
       </c>
       <c r="I13">
-        <v>214791571.522</v>
+        <v>214930933.245</v>
       </c>
       <c r="J13">
-        <v>204760889.896</v>
+        <v>204852766.189</v>
       </c>
       <c r="K13">
-        <v>225132942.978</v>
+        <v>225187974.151</v>
       </c>
       <c r="L13">
-        <v>736224090.4960001</v>
+        <v>735994789.3049999</v>
       </c>
       <c r="M13">
-        <v>701141970.26</v>
+        <v>700943742.7079999</v>
       </c>
       <c r="N13">
-        <v>772020212.999</v>
+        <v>771696261.975</v>
       </c>
     </row>
     <row r="14">
@@ -1014,40 +1014,40 @@
         </is>
       </c>
       <c r="C14">
-        <v>5652.014</v>
+        <v>5647.96</v>
       </c>
       <c r="D14">
-        <v>5225.951</v>
+        <v>5223.401</v>
       </c>
       <c r="E14">
-        <v>6080.491</v>
+        <v>6075.124</v>
       </c>
       <c r="F14">
-        <v>8301.268</v>
+        <v>8304.058000000001</v>
       </c>
       <c r="G14">
-        <v>7789.203</v>
+        <v>7791.162</v>
       </c>
       <c r="H14">
-        <v>8821.91</v>
+        <v>8822.145</v>
       </c>
       <c r="I14">
-        <v>95168971.148</v>
+        <v>95109355.95200001</v>
       </c>
       <c r="J14">
-        <v>88030635.426</v>
+        <v>87965753.98800001</v>
       </c>
       <c r="K14">
-        <v>102420740.73</v>
+        <v>102309382.376</v>
       </c>
       <c r="L14">
-        <v>1103922100.682</v>
+        <v>1104315378.674</v>
       </c>
       <c r="M14">
-        <v>1035558803.883</v>
+        <v>1036121947.834</v>
       </c>
       <c r="N14">
-        <v>1173054857.567</v>
+        <v>1173220542.524</v>
       </c>
     </row>
     <row r="15">
@@ -1062,40 +1062,40 @@
         </is>
       </c>
       <c r="C15">
-        <v>4840.841</v>
+        <v>4841.688</v>
       </c>
       <c r="D15">
-        <v>4494.423</v>
+        <v>4496.071</v>
       </c>
       <c r="E15">
-        <v>5191.482</v>
+        <v>5191.449</v>
       </c>
       <c r="F15">
-        <v>7050.269</v>
+        <v>7061.502</v>
       </c>
       <c r="G15">
-        <v>6681.828</v>
+        <v>6692.834</v>
       </c>
       <c r="H15">
-        <v>7420.656</v>
+        <v>7433.612</v>
       </c>
       <c r="I15">
-        <v>81499836.241</v>
+        <v>81524213.735</v>
       </c>
       <c r="J15">
-        <v>75656671.972</v>
+        <v>75686695.094</v>
       </c>
       <c r="K15">
-        <v>87380463.645</v>
+        <v>87390658.435</v>
       </c>
       <c r="L15">
-        <v>937560730.003</v>
+        <v>939035787.398</v>
       </c>
       <c r="M15">
-        <v>888746131.1160001</v>
+        <v>890259950.41</v>
       </c>
       <c r="N15">
-        <v>987119560.789</v>
+        <v>988719998.467</v>
       </c>
     </row>
     <row r="16">
@@ -1110,40 +1110,40 @@
         </is>
       </c>
       <c r="C16">
-        <v>8970.040999999999</v>
+        <v>8970.282999999999</v>
       </c>
       <c r="D16">
-        <v>8333.397999999999</v>
+        <v>8334.875</v>
       </c>
       <c r="E16">
-        <v>9613.951999999999</v>
+        <v>9613.147000000001</v>
       </c>
       <c r="F16">
-        <v>13689.077</v>
+        <v>13691.3</v>
       </c>
       <c r="G16">
-        <v>12910.644</v>
+        <v>12914.683</v>
       </c>
       <c r="H16">
-        <v>14483.81</v>
+        <v>14482.396</v>
       </c>
       <c r="I16">
-        <v>151077450.603</v>
+        <v>151067898.399</v>
       </c>
       <c r="J16">
-        <v>140323859.292</v>
+        <v>140305590.327</v>
       </c>
       <c r="K16">
-        <v>161926715.559</v>
+        <v>161939949.123</v>
       </c>
       <c r="L16">
-        <v>1820839129.458</v>
+        <v>1821263076.572</v>
       </c>
       <c r="M16">
-        <v>1716878573.354</v>
+        <v>1717246000.472</v>
       </c>
       <c r="N16">
-        <v>1926294735.775</v>
+        <v>1926063446.478</v>
       </c>
     </row>
     <row r="17">
@@ -1158,22 +1158,22 @@
         </is>
       </c>
       <c r="C17">
-        <v>32873.227</v>
+        <v>27426.414</v>
       </c>
       <c r="D17">
-        <v>31604.543</v>
+        <v>26318.163</v>
       </c>
       <c r="E17">
-        <v>34156.189</v>
+        <v>28546.298</v>
       </c>
       <c r="F17">
-        <v>75778.171</v>
+        <v>7103.635</v>
       </c>
       <c r="G17">
-        <v>71987.245</v>
+        <v>6736.053</v>
       </c>
       <c r="H17">
-        <v>79649.45699999999</v>
+        <v>7476.903</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -1185,13 +1185,13 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>10079865604.794</v>
+        <v>944781654.274</v>
       </c>
       <c r="M17">
-        <v>9572476115.906</v>
+        <v>896002776.7180001</v>
       </c>
       <c r="N17">
-        <v>10592378497.181</v>
+        <v>994473127.881</v>
       </c>
     </row>
     <row r="18">
@@ -1206,22 +1206,22 @@
         </is>
       </c>
       <c r="C18">
-        <v>28794.877</v>
+        <v>23996.762</v>
       </c>
       <c r="D18">
-        <v>27816.387</v>
+        <v>23144.064</v>
       </c>
       <c r="E18">
-        <v>29768.582</v>
+        <v>24850.999</v>
       </c>
       <c r="F18">
-        <v>70449.086</v>
+        <v>6570.413</v>
       </c>
       <c r="G18">
-        <v>67182.319</v>
+        <v>6262.865</v>
       </c>
       <c r="H18">
-        <v>73748.41</v>
+        <v>6884.054</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -1233,13 +1233,13 @@
         <v>0</v>
       </c>
       <c r="L18">
-        <v>9370635874.539</v>
+        <v>873994289.244</v>
       </c>
       <c r="M18">
-        <v>8938037262.905001</v>
+        <v>832998453.474</v>
       </c>
       <c r="N18">
-        <v>9810421995.368999</v>
+        <v>915761475.63</v>
       </c>
     </row>
     <row r="19">
@@ -1254,22 +1254,22 @@
         </is>
       </c>
       <c r="C19">
-        <v>71792.614</v>
+        <v>59616.624</v>
       </c>
       <c r="D19">
-        <v>69510.573</v>
+        <v>57635.917</v>
       </c>
       <c r="E19">
-        <v>74078.359</v>
+        <v>61611.321</v>
       </c>
       <c r="F19">
-        <v>202806.442</v>
+        <v>18689.638</v>
       </c>
       <c r="G19">
-        <v>194098.464</v>
+        <v>17868.722</v>
       </c>
       <c r="H19">
-        <v>211605.58</v>
+        <v>19520.435</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -1281,13 +1281,13 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>26974313788.706</v>
+        <v>2486034792.805</v>
       </c>
       <c r="M19">
-        <v>25826974937.458</v>
+        <v>2377350083.719</v>
       </c>
       <c r="N19">
-        <v>28139834197.383</v>
+        <v>2596153538.155</v>
       </c>
     </row>
     <row r="20">
@@ -1297,40 +1297,40 @@
         </is>
       </c>
       <c r="C20">
-        <v>239182.352</v>
+        <v>216808.223</v>
       </c>
       <c r="D20">
-        <v>228984.816</v>
+        <v>207196.317</v>
       </c>
       <c r="E20">
-        <v>249463.644</v>
+        <v>226522.448</v>
       </c>
       <c r="F20">
-        <v>468110.028</v>
+        <v>151548.181</v>
       </c>
       <c r="G20">
-        <v>446361.802</v>
+        <v>144064.503</v>
       </c>
       <c r="H20">
-        <v>490165.785</v>
+        <v>159156.035</v>
       </c>
       <c r="I20">
-        <v>4095026074.326</v>
+        <v>4097679250.849</v>
       </c>
       <c r="J20">
-        <v>3878728737.181</v>
+        <v>3881194946.141</v>
       </c>
       <c r="K20">
-        <v>4313678249.552999</v>
+        <v>4316861020.215999</v>
       </c>
       <c r="L20">
-        <v>62261897169.755</v>
+        <v>20156354913.814</v>
       </c>
       <c r="M20">
-        <v>59378380065.554</v>
+        <v>19161653360.355</v>
       </c>
       <c r="N20">
-        <v>65188174789.85599</v>
+        <v>21168227594.323</v>
       </c>
     </row>
     <row r="21">
@@ -1340,40 +1340,40 @@
         </is>
       </c>
       <c r="C21">
-        <v>336107.3589999999</v>
+        <v>313741.485</v>
       </c>
       <c r="D21">
-        <v>319459.276</v>
+        <v>297682.0810000001</v>
       </c>
       <c r="E21">
-        <v>352822.2719999999</v>
+        <v>329886.765</v>
       </c>
       <c r="F21">
-        <v>1377765.005</v>
+        <v>1061234.255</v>
       </c>
       <c r="G21">
-        <v>1321163.09</v>
+        <v>1018929.016</v>
       </c>
       <c r="H21">
-        <v>1434658.434</v>
+        <v>1103714.89</v>
       </c>
       <c r="I21">
-        <v>4095026074.326</v>
+        <v>4097679250.849</v>
       </c>
       <c r="J21">
-        <v>3878728737.181</v>
+        <v>3881194946.141</v>
       </c>
       <c r="K21">
-        <v>4313678249.552999</v>
+        <v>4316861020.215999</v>
       </c>
       <c r="L21">
-        <v>183251256972.732</v>
+        <v>141152148340.465</v>
       </c>
       <c r="M21">
-        <v>175721097858.261</v>
+        <v>135502842745.658</v>
       </c>
       <c r="N21">
-        <v>190837506334.796</v>
+        <v>146828614109.443</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/Best practice/Residence/HIA_best_practice_1000replicate_RES.xlsx
+++ b/output/Tables/Best practice/Residence/HIA_best_practice_1000replicate_RES.xlsx
@@ -438,22 +438,22 @@
         </is>
       </c>
       <c r="C2">
-        <v>29176.23</v>
+        <v>34049.409</v>
       </c>
       <c r="D2">
-        <v>27088.379</v>
+        <v>31641.343</v>
       </c>
       <c r="E2">
-        <v>31267.245</v>
+        <v>36462.905</v>
       </c>
       <c r="F2">
-        <v>253133.959</v>
+        <v>308698.565</v>
       </c>
       <c r="G2">
-        <v>242201.034</v>
+        <v>295683.071</v>
       </c>
       <c r="H2">
-        <v>264095.48</v>
+        <v>321730.497</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -465,13 +465,13 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>33667455071.95</v>
+        <v>41056520139.482</v>
       </c>
       <c r="M2">
-        <v>32208838105.116</v>
+        <v>39324435939.413</v>
       </c>
       <c r="N2">
-        <v>35122854057.599</v>
+        <v>42788150076.078</v>
       </c>
     </row>
     <row r="3">
@@ -486,22 +486,22 @@
         </is>
       </c>
       <c r="C3">
-        <v>27789.281</v>
+        <v>30892.621</v>
       </c>
       <c r="D3">
-        <v>26006.518</v>
+        <v>28952.467</v>
       </c>
       <c r="E3">
-        <v>29562.536</v>
+        <v>32820.011</v>
       </c>
       <c r="F3">
-        <v>251607.939</v>
+        <v>291691.451</v>
       </c>
       <c r="G3">
-        <v>242294.403</v>
+        <v>281081.82</v>
       </c>
       <c r="H3">
-        <v>260900.023</v>
+        <v>302293.371</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -513,13 +513,13 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>33461688390.11</v>
+        <v>38793008567.954</v>
       </c>
       <c r="M3">
-        <v>32221119532.697</v>
+        <v>37378154366.943</v>
       </c>
       <c r="N3">
-        <v>34710302221.23</v>
+        <v>40217566983.298</v>
       </c>
     </row>
     <row r="4">
@@ -534,22 +534,22 @@
         </is>
       </c>
       <c r="C4">
-        <v>39967.751</v>
+        <v>34856.981</v>
       </c>
       <c r="D4">
-        <v>37390.867</v>
+        <v>32706.019</v>
       </c>
       <c r="E4">
-        <v>42534.536</v>
+        <v>36998.416</v>
       </c>
       <c r="F4">
-        <v>404944.176</v>
+        <v>374763.56</v>
       </c>
       <c r="G4">
-        <v>390369.076</v>
+        <v>361438.191</v>
       </c>
       <c r="H4">
-        <v>419563.352</v>
+        <v>388100.677</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -561,13 +561,13 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>53866649964.591</v>
+        <v>49851959804.593</v>
       </c>
       <c r="M4">
-        <v>51911231747.49</v>
+        <v>48065294642.788</v>
       </c>
       <c r="N4">
-        <v>55827230236.291</v>
+        <v>51641150657.794</v>
       </c>
     </row>
     <row r="5">
@@ -582,40 +582,40 @@
         </is>
       </c>
       <c r="C5">
-        <v>15213.58</v>
+        <v>19522.368</v>
       </c>
       <c r="D5">
-        <v>14358.14</v>
+        <v>18429.798</v>
       </c>
       <c r="E5">
-        <v>16080.12</v>
+        <v>20629.758</v>
       </c>
       <c r="F5">
-        <v>11814.665</v>
+        <v>15535.261</v>
       </c>
       <c r="G5">
-        <v>11206.827</v>
+        <v>14755.984</v>
       </c>
       <c r="H5">
-        <v>12428.765</v>
+        <v>16322.338</v>
       </c>
       <c r="I5">
-        <v>847463911.3380001</v>
+        <v>1087509723.915</v>
       </c>
       <c r="J5">
-        <v>799699341.012</v>
+        <v>1026502557.435</v>
       </c>
       <c r="K5">
-        <v>895560733.051</v>
+        <v>1148957113.77</v>
       </c>
       <c r="L5">
-        <v>1571338018.892</v>
+        <v>2066150897.081</v>
       </c>
       <c r="M5">
-        <v>1490599066.52</v>
+        <v>1962729276.563</v>
       </c>
       <c r="N5">
-        <v>1652932821.965</v>
+        <v>2170818141.95</v>
       </c>
     </row>
     <row r="6">
@@ -630,40 +630,40 @@
         </is>
       </c>
       <c r="C6">
-        <v>13435.807</v>
+        <v>15629.423</v>
       </c>
       <c r="D6">
-        <v>12769.084</v>
+        <v>14864.087</v>
       </c>
       <c r="E6">
-        <v>14110.095</v>
+        <v>16403.455</v>
       </c>
       <c r="F6">
-        <v>10749.918</v>
+        <v>12847.594</v>
       </c>
       <c r="G6">
-        <v>10259.918</v>
+        <v>12273.394</v>
       </c>
       <c r="H6">
-        <v>11247.499</v>
+        <v>13431.71</v>
       </c>
       <c r="I6">
-        <v>748526928.141</v>
+        <v>870706606.089</v>
       </c>
       <c r="J6">
-        <v>711414814.402</v>
+        <v>828088414.568</v>
       </c>
       <c r="K6">
-        <v>786054082.812</v>
+        <v>913804891.925</v>
       </c>
       <c r="L6">
-        <v>1429817786.404</v>
+        <v>1708827181.884</v>
       </c>
       <c r="M6">
-        <v>1364589783.668</v>
+        <v>1632379050.51</v>
       </c>
       <c r="N6">
-        <v>1495956502.87</v>
+        <v>1786480557.537</v>
       </c>
     </row>
     <row r="7">
@@ -678,40 +678,40 @@
         </is>
       </c>
       <c r="C7">
-        <v>24041.56</v>
+        <v>19540.313</v>
       </c>
       <c r="D7">
-        <v>22822.8</v>
+        <v>18587.38</v>
       </c>
       <c r="E7">
-        <v>25276.5</v>
+        <v>20505.26</v>
       </c>
       <c r="F7">
-        <v>20368.632</v>
+        <v>17642.669</v>
       </c>
       <c r="G7">
-        <v>19479.353</v>
+        <v>16890.77</v>
       </c>
       <c r="H7">
-        <v>21265.563</v>
+        <v>18401.59</v>
       </c>
       <c r="I7">
-        <v>1339193519.068</v>
+        <v>1088430310.521</v>
       </c>
       <c r="J7">
-        <v>1270940002.323</v>
+        <v>1035056644.269</v>
       </c>
       <c r="K7">
-        <v>1408410092.38</v>
+        <v>1142498325.722</v>
       </c>
       <c r="L7">
-        <v>2709160040.966</v>
+        <v>2346637565.489</v>
       </c>
       <c r="M7">
-        <v>2590790931.532</v>
+        <v>2246530620.074</v>
       </c>
       <c r="N7">
-        <v>2828960507.208</v>
+        <v>2447903960.216</v>
       </c>
     </row>
     <row r="8">
@@ -726,40 +726,40 @@
         </is>
       </c>
       <c r="C8">
-        <v>7445.826</v>
+        <v>10515.488</v>
       </c>
       <c r="D8">
-        <v>7075.912</v>
+        <v>10003.627</v>
       </c>
       <c r="E8">
-        <v>7823.749</v>
+        <v>11039.813</v>
       </c>
       <c r="F8">
-        <v>8887.757</v>
+        <v>13572.93</v>
       </c>
       <c r="G8">
-        <v>8400.766</v>
+        <v>12795.847</v>
       </c>
       <c r="H8">
-        <v>9391.992</v>
+        <v>14384.945</v>
       </c>
       <c r="I8">
-        <v>110226530.035</v>
+        <v>155674252.981</v>
       </c>
       <c r="J8">
-        <v>104777336.802</v>
+        <v>148116429.745</v>
       </c>
       <c r="K8">
-        <v>115811243.351</v>
+        <v>163421607.115</v>
       </c>
       <c r="L8">
-        <v>1182009748.605</v>
+        <v>1805043633.704</v>
       </c>
       <c r="M8">
-        <v>1117053942.812</v>
+        <v>1701699773.74</v>
       </c>
       <c r="N8">
-        <v>1249239710.325</v>
+        <v>1912896347.35</v>
       </c>
     </row>
     <row r="9">
@@ -774,40 +774,40 @@
         </is>
       </c>
       <c r="C9">
-        <v>6389.522</v>
+        <v>7888.195</v>
       </c>
       <c r="D9">
-        <v>6111.595</v>
+        <v>7550.356</v>
       </c>
       <c r="E9">
-        <v>6669.555</v>
+        <v>8227.514999999999</v>
       </c>
       <c r="F9">
-        <v>7909.374</v>
+        <v>10158.23</v>
       </c>
       <c r="G9">
-        <v>7525.415</v>
+        <v>9657.742</v>
       </c>
       <c r="H9">
-        <v>8301.477999999999</v>
+        <v>10670.856</v>
       </c>
       <c r="I9">
-        <v>94604018.388</v>
+        <v>116793443.135</v>
       </c>
       <c r="J9">
-        <v>90503068.92200001</v>
+        <v>111818763.883</v>
       </c>
       <c r="K9">
-        <v>98764991.411</v>
+        <v>121848043.361</v>
       </c>
       <c r="L9">
-        <v>1051885432.585</v>
+        <v>1351001949.337</v>
       </c>
       <c r="M9">
-        <v>1000698244.372</v>
+        <v>1284083548.561</v>
       </c>
       <c r="N9">
-        <v>1104344649.063</v>
+        <v>1419347434.618</v>
       </c>
     </row>
     <row r="10">
@@ -822,40 +822,40 @@
         </is>
       </c>
       <c r="C10">
-        <v>14201.711</v>
+        <v>12202.606</v>
       </c>
       <c r="D10">
-        <v>13608.942</v>
+        <v>11702.076</v>
       </c>
       <c r="E10">
-        <v>14804.059</v>
+        <v>12710.426</v>
       </c>
       <c r="F10">
-        <v>20252.04</v>
+        <v>18668.542</v>
       </c>
       <c r="G10">
-        <v>19294.185</v>
+        <v>17767.994</v>
       </c>
       <c r="H10">
-        <v>21230.882</v>
+        <v>19590.188</v>
       </c>
       <c r="I10">
-        <v>210285071.55</v>
+        <v>180683209.155</v>
       </c>
       <c r="J10">
-        <v>201525769.428</v>
+        <v>173307352.39</v>
       </c>
       <c r="K10">
-        <v>219238264.121</v>
+        <v>188221866.05</v>
       </c>
       <c r="L10">
-        <v>2693489628.516</v>
+        <v>2482826348.173</v>
       </c>
       <c r="M10">
-        <v>2566945132.571</v>
+        <v>2363795781.389</v>
       </c>
       <c r="N10">
-        <v>2823252581.91</v>
+        <v>2605166073.858</v>
       </c>
     </row>
     <row r="11">
@@ -870,40 +870,40 @@
         </is>
       </c>
       <c r="C11">
-        <v>1448.396</v>
+        <v>2061.315</v>
       </c>
       <c r="D11">
-        <v>1364.578</v>
+        <v>1947.545</v>
       </c>
       <c r="E11">
-        <v>1535.15</v>
+        <v>2179.217</v>
       </c>
       <c r="F11">
-        <v>2413.044</v>
+        <v>3637.914</v>
       </c>
       <c r="G11">
-        <v>2275.871</v>
+        <v>3432.431</v>
       </c>
       <c r="H11">
-        <v>2555.936</v>
+        <v>3851.968</v>
       </c>
       <c r="I11">
-        <v>108931845.393</v>
+        <v>155028017.311</v>
       </c>
       <c r="J11">
-        <v>102592522.849</v>
+        <v>146404317.481</v>
       </c>
       <c r="K11">
-        <v>115413891.95</v>
+        <v>163824978.991</v>
       </c>
       <c r="L11">
-        <v>320944308.248</v>
+        <v>483855512.778</v>
       </c>
       <c r="M11">
-        <v>302596146.279</v>
+        <v>456413429.3</v>
       </c>
       <c r="N11">
-        <v>339952237.555</v>
+        <v>512324804.105</v>
       </c>
     </row>
     <row r="12">
@@ -918,40 +918,40 @@
         </is>
       </c>
       <c r="C12">
-        <v>1274.001</v>
+        <v>1589.586</v>
       </c>
       <c r="D12">
-        <v>1208.759</v>
+        <v>1509.83</v>
       </c>
       <c r="E12">
-        <v>1340.305</v>
+        <v>1670.534</v>
       </c>
       <c r="F12">
-        <v>2197.96</v>
+        <v>2817.139</v>
       </c>
       <c r="G12">
-        <v>2086.047</v>
+        <v>2673.513</v>
       </c>
       <c r="H12">
-        <v>2311.59</v>
+        <v>2963.291</v>
       </c>
       <c r="I12">
-        <v>95815025.605</v>
+        <v>119551979.618</v>
       </c>
       <c r="J12">
-        <v>90931284.80500001</v>
+        <v>113582967.64</v>
       </c>
       <c r="K12">
-        <v>100779757.055</v>
+        <v>125621285.018</v>
       </c>
       <c r="L12">
-        <v>292290181.326</v>
+        <v>374643304.057</v>
       </c>
       <c r="M12">
-        <v>277457157.266</v>
+        <v>355596299.421</v>
       </c>
       <c r="N12">
-        <v>307500192.317</v>
+        <v>394125231.016</v>
       </c>
     </row>
     <row r="13">
@@ -966,40 +966,40 @@
         </is>
       </c>
       <c r="C13">
-        <v>2858.089</v>
+        <v>2502.239</v>
       </c>
       <c r="D13">
-        <v>2724.016</v>
+        <v>2385.756</v>
       </c>
       <c r="E13">
-        <v>2994.577</v>
+        <v>2620.712</v>
       </c>
       <c r="F13">
-        <v>5534.245</v>
+        <v>5079.879</v>
       </c>
       <c r="G13">
-        <v>5269.802</v>
+        <v>4835.147</v>
       </c>
       <c r="H13">
-        <v>5802.785</v>
+        <v>5328.369</v>
       </c>
       <c r="I13">
-        <v>214930933.245</v>
+        <v>188172838.929</v>
       </c>
       <c r="J13">
-        <v>204852766.189</v>
+        <v>179419234.869</v>
       </c>
       <c r="K13">
-        <v>225187974.151</v>
+        <v>197076931.247</v>
       </c>
       <c r="L13">
-        <v>735994789.3049999</v>
+        <v>675557738.554</v>
       </c>
       <c r="M13">
-        <v>700943742.7079999</v>
+        <v>643040953.012</v>
       </c>
       <c r="N13">
-        <v>771696261.975</v>
+        <v>708641003.199</v>
       </c>
     </row>
     <row r="14">
@@ -1014,40 +1014,40 @@
         </is>
       </c>
       <c r="C14">
-        <v>5647.96</v>
+        <v>7213.704</v>
       </c>
       <c r="D14">
-        <v>5223.401</v>
+        <v>6674.728</v>
       </c>
       <c r="E14">
-        <v>6075.124</v>
+        <v>7755.744</v>
       </c>
       <c r="F14">
-        <v>8304.058000000001</v>
+        <v>10776.984</v>
       </c>
       <c r="G14">
-        <v>7791.162</v>
+        <v>10110.024</v>
       </c>
       <c r="H14">
-        <v>8822.145</v>
+        <v>11452.362</v>
       </c>
       <c r="I14">
-        <v>95109355.95200001</v>
+        <v>121477420.73</v>
       </c>
       <c r="J14">
-        <v>87965753.98800001</v>
+        <v>112414274.203</v>
       </c>
       <c r="K14">
-        <v>102309382.376</v>
+        <v>130611981.111</v>
       </c>
       <c r="L14">
-        <v>1104315378.674</v>
+        <v>1433187243.799</v>
       </c>
       <c r="M14">
-        <v>1036121947.834</v>
+        <v>1344550931.643</v>
       </c>
       <c r="N14">
-        <v>1173220542.524</v>
+        <v>1522907246.314</v>
       </c>
     </row>
     <row r="15">
@@ -1062,40 +1062,40 @@
         </is>
       </c>
       <c r="C15">
-        <v>4841.688</v>
+        <v>5565.41</v>
       </c>
       <c r="D15">
-        <v>4496.071</v>
+        <v>5172.745</v>
       </c>
       <c r="E15">
-        <v>5191.449</v>
+        <v>5963.294</v>
       </c>
       <c r="F15">
-        <v>7061.502</v>
+        <v>8304.186</v>
       </c>
       <c r="G15">
-        <v>6692.834</v>
+        <v>7874.326</v>
       </c>
       <c r="H15">
-        <v>7433.612</v>
+        <v>8737.806</v>
       </c>
       <c r="I15">
-        <v>81524213.735</v>
+        <v>93710939.579</v>
       </c>
       <c r="J15">
-        <v>75686695.094</v>
+        <v>87085376.517</v>
       </c>
       <c r="K15">
-        <v>87390658.435</v>
+        <v>100379221.359</v>
       </c>
       <c r="L15">
-        <v>939035787.398</v>
+        <v>1104282255.817</v>
       </c>
       <c r="M15">
-        <v>890259950.41</v>
+        <v>1047514511.451</v>
       </c>
       <c r="N15">
-        <v>988719998.467</v>
+        <v>1162164992.642</v>
       </c>
     </row>
     <row r="16">
@@ -1110,40 +1110,40 @@
         </is>
       </c>
       <c r="C16">
-        <v>8970.282999999999</v>
+        <v>6906.579</v>
       </c>
       <c r="D16">
-        <v>8334.875</v>
+        <v>6439.128</v>
       </c>
       <c r="E16">
-        <v>9613.147000000001</v>
+        <v>7379.192</v>
       </c>
       <c r="F16">
-        <v>13691.3</v>
+        <v>11261.063</v>
       </c>
       <c r="G16">
-        <v>12914.683</v>
+        <v>10637.399</v>
       </c>
       <c r="H16">
-        <v>14482.396</v>
+        <v>11896.311</v>
       </c>
       <c r="I16">
-        <v>151067898.399</v>
+        <v>116314411.592</v>
       </c>
       <c r="J16">
-        <v>140305590.327</v>
+        <v>108394180.913</v>
       </c>
       <c r="K16">
-        <v>161939949.123</v>
+        <v>124312662.065</v>
       </c>
       <c r="L16">
-        <v>1821263076.572</v>
+        <v>1497944344.905</v>
       </c>
       <c r="M16">
-        <v>1717246000.472</v>
+        <v>1414513897.945</v>
       </c>
       <c r="N16">
-        <v>1926063446.478</v>
+        <v>1582087740.092</v>
       </c>
     </row>
     <row r="17">
@@ -1158,22 +1158,22 @@
         </is>
       </c>
       <c r="C17">
-        <v>27426.414</v>
+        <v>40472.983</v>
       </c>
       <c r="D17">
-        <v>26318.163</v>
+        <v>38821.135</v>
       </c>
       <c r="E17">
-        <v>28546.298</v>
+        <v>42148.516</v>
       </c>
       <c r="F17">
-        <v>7103.635</v>
+        <v>11432.064</v>
       </c>
       <c r="G17">
-        <v>6736.053</v>
+        <v>10792.565</v>
       </c>
       <c r="H17">
-        <v>7476.903</v>
+        <v>12084.547</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -1185,13 +1185,13 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>944781654.274</v>
+        <v>1520471945.813</v>
       </c>
       <c r="M17">
-        <v>896002776.7180001</v>
+        <v>1435656257.882</v>
       </c>
       <c r="N17">
-        <v>994473127.881</v>
+        <v>1607322757.135</v>
       </c>
     </row>
     <row r="18">
@@ -1206,22 +1206,22 @@
         </is>
       </c>
       <c r="C18">
-        <v>23996.762</v>
+        <v>30091.127</v>
       </c>
       <c r="D18">
-        <v>23144.064</v>
+        <v>29029.478</v>
       </c>
       <c r="E18">
-        <v>24850.999</v>
+        <v>31157.65</v>
       </c>
       <c r="F18">
-        <v>6570.413</v>
+        <v>8482.531000000001</v>
       </c>
       <c r="G18">
-        <v>6262.865</v>
+        <v>8086.008</v>
       </c>
       <c r="H18">
-        <v>6884.054</v>
+        <v>8886.552</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -1233,13 +1233,13 @@
         <v>0</v>
       </c>
       <c r="L18">
-        <v>873994289.244</v>
+        <v>1128339741.959</v>
       </c>
       <c r="M18">
-        <v>832998453.474</v>
+        <v>1075408459.946</v>
       </c>
       <c r="N18">
-        <v>915761475.63</v>
+        <v>1182139869.437</v>
       </c>
     </row>
     <row r="19">
@@ -1254,22 +1254,22 @@
         </is>
       </c>
       <c r="C19">
-        <v>59616.624</v>
+        <v>53804.46</v>
       </c>
       <c r="D19">
-        <v>57635.917</v>
+        <v>51975.673</v>
       </c>
       <c r="E19">
-        <v>61611.321</v>
+        <v>55645.687</v>
       </c>
       <c r="F19">
-        <v>18689.638</v>
+        <v>17973.893</v>
       </c>
       <c r="G19">
-        <v>17868.722</v>
+        <v>17143.719</v>
       </c>
       <c r="H19">
-        <v>19520.435</v>
+        <v>18816.164</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -1281,13 +1281,13 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>2486034792.805</v>
+        <v>2390829625.806</v>
       </c>
       <c r="M19">
-        <v>2377350083.719</v>
+        <v>2280890956.502</v>
       </c>
       <c r="N19">
-        <v>2596153538.155</v>
+        <v>2502589681.858</v>
       </c>
     </row>
     <row r="20">
@@ -1297,40 +1297,40 @@
         </is>
       </c>
       <c r="C20">
-        <v>216808.223</v>
+        <v>235505.796</v>
       </c>
       <c r="D20">
-        <v>207196.317</v>
+        <v>225093.342</v>
       </c>
       <c r="E20">
-        <v>226522.448</v>
+        <v>246036.773</v>
       </c>
       <c r="F20">
-        <v>151548.181</v>
+        <v>168190.879</v>
       </c>
       <c r="G20">
-        <v>144064.503</v>
+        <v>159726.863</v>
       </c>
       <c r="H20">
-        <v>159156.035</v>
+        <v>176818.9969999999</v>
       </c>
       <c r="I20">
-        <v>4097679250.849</v>
+        <v>4294053153.555</v>
       </c>
       <c r="J20">
-        <v>3881194946.141</v>
+        <v>4070190513.913</v>
       </c>
       <c r="K20">
-        <v>4316861020.215999</v>
+        <v>4520578907.734</v>
       </c>
       <c r="L20">
-        <v>20156354913.814</v>
+        <v>22369599289.156</v>
       </c>
       <c r="M20">
-        <v>19161653360.355</v>
+        <v>21244803747.939</v>
       </c>
       <c r="N20">
-        <v>21168227594.323</v>
+        <v>23516915841.327</v>
       </c>
     </row>
     <row r="21">
@@ -1340,40 +1340,40 @@
         </is>
       </c>
       <c r="C21">
-        <v>313741.485</v>
+        <v>335304.807</v>
       </c>
       <c r="D21">
-        <v>297682.0810000001</v>
+        <v>318393.171</v>
       </c>
       <c r="E21">
-        <v>329886.765</v>
+        <v>352318.105</v>
       </c>
       <c r="F21">
-        <v>1061234.255</v>
+        <v>1143344.455</v>
       </c>
       <c r="G21">
-        <v>1018929.016</v>
+        <v>1097929.945</v>
       </c>
       <c r="H21">
-        <v>1103714.89</v>
+        <v>1188943.542</v>
       </c>
       <c r="I21">
-        <v>4097679250.849</v>
+        <v>4294053153.555</v>
       </c>
       <c r="J21">
-        <v>3881194946.141</v>
+        <v>4070190513.913</v>
       </c>
       <c r="K21">
-        <v>4316861020.215999</v>
+        <v>4520578907.734</v>
       </c>
       <c r="L21">
-        <v>141152148340.465</v>
+        <v>152071087801.185</v>
       </c>
       <c r="M21">
-        <v>135502842745.658</v>
+        <v>146012688697.083</v>
       </c>
       <c r="N21">
-        <v>146828614109.443</v>
+        <v>158163783558.4971</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/Best practice/Residence/HIA_best_practice_1000replicate_RES.xlsx
+++ b/output/Tables/Best practice/Residence/HIA_best_practice_1000replicate_RES.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:N30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1293,87 +1293,529 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Morbidity</t>
+          <t>cancer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>All</t>
         </is>
       </c>
       <c r="C20">
-        <v>235505.796</v>
+        <v>30606.289</v>
       </c>
       <c r="D20">
-        <v>225093.342</v>
+        <v>29256.059</v>
       </c>
       <c r="E20">
-        <v>246036.773</v>
+        <v>31977.754</v>
       </c>
       <c r="F20">
-        <v>168190.879</v>
+        <v>42399.702</v>
       </c>
       <c r="G20">
-        <v>159726.863</v>
+        <v>40221.583</v>
       </c>
       <c r="H20">
-        <v>176818.9969999999</v>
+        <v>44645.989</v>
       </c>
       <c r="I20">
-        <v>4294053153.555</v>
+        <v>453150905.271</v>
       </c>
       <c r="J20">
-        <v>4070190513.913</v>
+        <v>433242546.018</v>
       </c>
       <c r="K20">
-        <v>4520578907.734</v>
+        <v>473491516.526</v>
       </c>
       <c r="L20">
-        <v>22369599289.156</v>
+        <v>5638871931.214</v>
       </c>
       <c r="M20">
-        <v>21244803747.939</v>
+        <v>5349579103.690001</v>
       </c>
       <c r="N20">
-        <v>23516915841.327</v>
+        <v>5937409855.826</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>cvd</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>All</t>
         </is>
       </c>
       <c r="C21">
+        <v>54692.10399999999</v>
+      </c>
+      <c r="D21">
+        <v>51881.265</v>
+      </c>
+      <c r="E21">
+        <v>57538.473</v>
+      </c>
+      <c r="F21">
+        <v>46025.524</v>
+      </c>
+      <c r="G21">
+        <v>43920.148</v>
+      </c>
+      <c r="H21">
+        <v>48155.638</v>
+      </c>
+      <c r="I21">
+        <v>3046646640.525</v>
+      </c>
+      <c r="J21">
+        <v>2889647616.272</v>
+      </c>
+      <c r="K21">
+        <v>3205260331.417</v>
+      </c>
+      <c r="L21">
+        <v>6121615644.454</v>
+      </c>
+      <c r="M21">
+        <v>5841638947.146999</v>
+      </c>
+      <c r="N21">
+        <v>6405202659.702999</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>dem</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>19685.693</v>
+      </c>
+      <c r="D22">
+        <v>18286.601</v>
+      </c>
+      <c r="E22">
+        <v>21098.23</v>
+      </c>
+      <c r="F22">
+        <v>30342.233</v>
+      </c>
+      <c r="G22">
+        <v>28621.749</v>
+      </c>
+      <c r="H22">
+        <v>32086.479</v>
+      </c>
+      <c r="I22">
+        <v>331502771.901</v>
+      </c>
+      <c r="J22">
+        <v>307893831.633</v>
+      </c>
+      <c r="K22">
+        <v>355303864.535</v>
+      </c>
+      <c r="L22">
+        <v>4035413844.521</v>
+      </c>
+      <c r="M22">
+        <v>3806579341.039</v>
+      </c>
+      <c r="N22">
+        <v>4267159979.048</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>dep</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>124368.57</v>
+      </c>
+      <c r="D23">
+        <v>119826.286</v>
+      </c>
+      <c r="E23">
+        <v>128951.853</v>
+      </c>
+      <c r="F23">
+        <v>37888.488</v>
+      </c>
+      <c r="G23">
+        <v>36022.292</v>
+      </c>
+      <c r="H23">
+        <v>39787.26300000001</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>5039641313.578001</v>
+      </c>
+      <c r="M23">
+        <v>4791955674.33</v>
+      </c>
+      <c r="N23">
+        <v>5292052308.43</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>diab2</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>6153.139999999999</v>
+      </c>
+      <c r="D24">
+        <v>5843.130999999999</v>
+      </c>
+      <c r="E24">
+        <v>6470.463</v>
+      </c>
+      <c r="F24">
+        <v>11534.932</v>
+      </c>
+      <c r="G24">
+        <v>10941.091</v>
+      </c>
+      <c r="H24">
+        <v>12143.628</v>
+      </c>
+      <c r="I24">
+        <v>462752835.858</v>
+      </c>
+      <c r="J24">
+        <v>439406519.99</v>
+      </c>
+      <c r="K24">
+        <v>486523195.256</v>
+      </c>
+      <c r="L24">
+        <v>1534056555.389</v>
+      </c>
+      <c r="M24">
+        <v>1455050681.733</v>
+      </c>
+      <c r="N24">
+        <v>1615091038.32</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>mort</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>99799.011</v>
+      </c>
+      <c r="D25">
+        <v>93299.829</v>
+      </c>
+      <c r="E25">
+        <v>106281.332</v>
+      </c>
+      <c r="F25">
+        <v>975153.5760000001</v>
+      </c>
+      <c r="G25">
+        <v>938203.0820000001</v>
+      </c>
+      <c r="H25">
+        <v>1012124.545</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>129701488512.029</v>
+      </c>
+      <c r="M25">
+        <v>124767884949.144</v>
+      </c>
+      <c r="N25">
+        <v>134646867717.17</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>periurban</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>113835.267</v>
+      </c>
+      <c r="D26">
+        <v>107518.176</v>
+      </c>
+      <c r="E26">
+        <v>120215.953</v>
+      </c>
+      <c r="F26">
+        <v>363653.718</v>
+      </c>
+      <c r="G26">
+        <v>347569.922</v>
+      </c>
+      <c r="H26">
+        <v>379826.657</v>
+      </c>
+      <c r="I26">
+        <v>1519689414.937</v>
+      </c>
+      <c r="J26">
+        <v>1433437578.864</v>
+      </c>
+      <c r="K26">
+        <v>1606815680.987</v>
+      </c>
+      <c r="L26">
+        <v>48365229372.65701</v>
+      </c>
+      <c r="M26">
+        <v>46225485608.541</v>
+      </c>
+      <c r="N26">
+        <v>50514419372.93201</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>rural</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>91656.36199999999</v>
+      </c>
+      <c r="D27">
+        <v>87078.963</v>
+      </c>
+      <c r="E27">
+        <v>96242.459</v>
+      </c>
+      <c r="F27">
+        <v>334301.131</v>
+      </c>
+      <c r="G27">
+        <v>321646.803</v>
+      </c>
+      <c r="H27">
+        <v>346983.5860000001</v>
+      </c>
+      <c r="I27">
+        <v>1200762968.421</v>
+      </c>
+      <c r="J27">
+        <v>1140575522.608</v>
+      </c>
+      <c r="K27">
+        <v>1261653441.663</v>
+      </c>
+      <c r="L27">
+        <v>44460103001.008</v>
+      </c>
+      <c r="M27">
+        <v>42773136236.83199</v>
+      </c>
+      <c r="N27">
+        <v>46161825068.548</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>urban</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>129813.178</v>
+      </c>
+      <c r="D28">
+        <v>123796.032</v>
+      </c>
+      <c r="E28">
+        <v>135859.693</v>
+      </c>
+      <c r="F28">
+        <v>445389.606</v>
+      </c>
+      <c r="G28">
+        <v>428713.22</v>
+      </c>
+      <c r="H28">
+        <v>462133.2990000001</v>
+      </c>
+      <c r="I28">
+        <v>1573600770.197</v>
+      </c>
+      <c r="J28">
+        <v>1496177412.441</v>
+      </c>
+      <c r="K28">
+        <v>1652109785.084</v>
+      </c>
+      <c r="L28">
+        <v>59245755427.52</v>
+      </c>
+      <c r="M28">
+        <v>57014066851.71</v>
+      </c>
+      <c r="N28">
+        <v>61487539117.01701</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C29">
         <v>335304.807</v>
       </c>
-      <c r="D21">
+      <c r="D29">
         <v>318393.171</v>
       </c>
-      <c r="E21">
+      <c r="E29">
         <v>352318.105</v>
       </c>
-      <c r="F21">
+      <c r="F29">
         <v>1143344.455</v>
       </c>
-      <c r="G21">
+      <c r="G29">
         <v>1097929.945</v>
       </c>
-      <c r="H21">
+      <c r="H29">
         <v>1188943.542</v>
       </c>
-      <c r="I21">
+      <c r="I29">
         <v>4294053153.555</v>
       </c>
-      <c r="J21">
+      <c r="J29">
         <v>4070190513.913</v>
       </c>
-      <c r="K21">
+      <c r="K29">
         <v>4520578907.734</v>
       </c>
-      <c r="L21">
+      <c r="L29">
         <v>152071087801.185</v>
       </c>
-      <c r="M21">
+      <c r="M29">
         <v>146012688697.083</v>
       </c>
-      <c r="N21">
+      <c r="N29">
         <v>158163783558.4971</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Morbidity</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>235505.796</v>
+      </c>
+      <c r="D30">
+        <v>225093.342</v>
+      </c>
+      <c r="E30">
+        <v>246036.773</v>
+      </c>
+      <c r="F30">
+        <v>168190.879</v>
+      </c>
+      <c r="G30">
+        <v>159726.863</v>
+      </c>
+      <c r="H30">
+        <v>176818.9969999999</v>
+      </c>
+      <c r="I30">
+        <v>4294053153.555</v>
+      </c>
+      <c r="J30">
+        <v>4070190513.913</v>
+      </c>
+      <c r="K30">
+        <v>4520578907.734</v>
+      </c>
+      <c r="L30">
+        <v>22369599289.156</v>
+      </c>
+      <c r="M30">
+        <v>21244803747.939</v>
+      </c>
+      <c r="N30">
+        <v>23516915841.327</v>
       </c>
     </row>
   </sheetData>
